--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O260"/>
+  <dimension ref="A1:O268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11471,10 +11471,10 @@
       </c>
       <c r="N188" s="5" t="inlineStr">
         <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="O188" s="2" t="inlineStr"/>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11528,10 +11528,10 @@
       </c>
       <c r="N189" s="5" t="inlineStr">
         <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="O189" s="2" t="inlineStr"/>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11585,10 +11585,10 @@
       </c>
       <c r="N190" s="5" t="inlineStr">
         <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="inlineStr"/>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -12368,25 +12368,29 @@
         <v>123</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.0048</v>
+        <v>0.0046</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O204" s="2" t="inlineStr"/>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>Updated 2026-03-26, was 5000CW</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -12425,25 +12429,29 @@
         <v>247</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.0008</v>
+        <v>0.0012</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
-        </is>
-      </c>
-      <c r="O205" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>Updated 2026-03-26, was 5000CW</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -12482,13 +12490,13 @@
         <v>493</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.0003333333333333333</v>
+        <v>0.0009</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="M206" s="4" t="inlineStr">
         <is>
@@ -12500,7 +12508,11 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O206" s="2" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>Updated 2026-03-26, was 3000CW</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -15633,6 +15645,494 @@
       <c r="O260" s="2" t="inlineStr">
         <is>
           <t>MLP z_encoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>8</v>
+      </c>
+      <c r="H261" t="n">
+        <v>4</v>
+      </c>
+      <c r="I261" t="n">
+        <v>2</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="K261" t="n">
+        <v>178</v>
+      </c>
+      <c r="L261" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>16</v>
+      </c>
+      <c r="H262" t="n">
+        <v>7</v>
+      </c>
+      <c r="I262" t="n">
+        <v>4</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="K262" t="n">
+        <v>119</v>
+      </c>
+      <c r="L262" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0.2188</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>32</v>
+      </c>
+      <c r="H263" t="n">
+        <v>15</v>
+      </c>
+      <c r="I263" t="n">
+        <v>7</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="K263" t="n">
+        <v>29</v>
+      </c>
+      <c r="L263" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>64</v>
+      </c>
+      <c r="H264" t="n">
+        <v>29</v>
+      </c>
+      <c r="I264" t="n">
+        <v>15</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K264" t="n">
+        <v>20</v>
+      </c>
+      <c r="L264" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>128</v>
+      </c>
+      <c r="H265" t="n">
+        <v>58</v>
+      </c>
+      <c r="I265" t="n">
+        <v>30</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>256</v>
+      </c>
+      <c r="H266" t="n">
+        <v>117</v>
+      </c>
+      <c r="I266" t="n">
+        <v>59</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="K266" t="n">
+        <v>4</v>
+      </c>
+      <c r="L266" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>512</v>
+      </c>
+      <c r="H267" t="n">
+        <v>233</v>
+      </c>
+      <c r="I267" t="n">
+        <v>119</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H268" t="n">
+        <v>467</v>
+      </c>
+      <c r="I268" t="n">
+        <v>238</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="K268" t="n">
+        <v>4</v>
+      </c>
+      <c r="L268" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>New SC baseline 2026-03-26</t>
         </is>
       </c>
     </row>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O268"/>
+  <dimension ref="A1:O275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16133,6 +16133,433 @@
       <c r="O268" t="inlineStr">
         <is>
           <t>New SC baseline 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>16</v>
+      </c>
+      <c r="H269" t="n">
+        <v>10</v>
+      </c>
+      <c r="I269" t="n">
+        <v>10</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K269" t="n">
+        <v>130</v>
+      </c>
+      <c r="L269" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>32</v>
+      </c>
+      <c r="H270" t="n">
+        <v>20</v>
+      </c>
+      <c r="I270" t="n">
+        <v>20</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="K270" t="n">
+        <v>136</v>
+      </c>
+      <c r="L270" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>64</v>
+      </c>
+      <c r="H271" t="n">
+        <v>40</v>
+      </c>
+      <c r="I271" t="n">
+        <v>40</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K271" t="n">
+        <v>60</v>
+      </c>
+      <c r="L271" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=24</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>128</v>
+      </c>
+      <c r="H272" t="n">
+        <v>79</v>
+      </c>
+      <c r="I272" t="n">
+        <v>79</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="K272" t="n">
+        <v>22</v>
+      </c>
+      <c r="L272" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=48</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>256</v>
+      </c>
+      <c r="H273" t="n">
+        <v>159</v>
+      </c>
+      <c r="I273" t="n">
+        <v>159</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K273" t="n">
+        <v>10</v>
+      </c>
+      <c r="L273" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=96</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>512</v>
+      </c>
+      <c r="H274" t="n">
+        <v>317</v>
+      </c>
+      <c r="I274" t="n">
+        <v>317</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="K274" t="n">
+        <v>7</v>
+      </c>
+      <c r="L274" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=192</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Pure Neural</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H275" t="n">
+        <v>635</v>
+      </c>
+      <c r="I275" t="n">
+        <v>635</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="K275" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>NN trained on Class B, tested on Class A; path_i=384</t>
         </is>
       </c>
     </row>
@@ -28694,7 +29121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30663,6 +31090,363 @@
       <c r="M38" s="4" t="inlineStr">
         <is>
           <t>ZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F40" t="n">
+        <v>32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F41" t="n">
+        <v>64</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="F42" t="n">
+        <v>128</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="F43" t="n">
+        <v>256</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="F44" t="n">
+        <v>512</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v/>
+      </c>
+      <c r="J45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>500</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
         </is>
       </c>
     </row>
@@ -30982,7 +31766,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2 days</t>
+          <t>DONE - NN matches SC, ratio 0.47-1.22, generalizes from Class B training</t>
         </is>
       </c>
     </row>
@@ -32840,7 +33624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -33113,6 +33897,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BEMAC NN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pure Neural decoder trained on Class B generalizes to Class A (Ru=Rv=0.62)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BLER ratios 0.47-1.22 across N=16-1024; NN beats SC at N=64,256,512 (ratios 0.85,0.80,0.47)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cross-class generalization validates that NeuralCalcParent learns universal polar code structure, not class-specific patterns</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O275"/>
+  <dimension ref="A1:O279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16560,6 +16560,230 @@
       <c r="O275" t="inlineStr">
         <is>
           <t>NN trained on Class B, tested on Class A; path_i=384</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>SCL-32</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>16</v>
+      </c>
+      <c r="H276" t="n">
+        <v>8</v>
+      </c>
+      <c r="I276" t="n">
+        <v>11</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K276" t="n">
+        <v>40</v>
+      </c>
+      <c r="L276" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SCL-32</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>32</v>
+      </c>
+      <c r="H277" t="n">
+        <v>16</v>
+      </c>
+      <c r="I277" t="n">
+        <v>22</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="K277" t="n">
+        <v>41</v>
+      </c>
+      <c r="L277" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>SCL-32</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>64</v>
+      </c>
+      <c r="H278" t="n">
+        <v>32</v>
+      </c>
+      <c r="I278" t="n">
+        <v>45</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K278" t="n">
+        <v>5</v>
+      </c>
+      <c r="L278" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>SCL-32</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>128</v>
+      </c>
+      <c r="H279" t="n">
+        <v>64</v>
+      </c>
+      <c r="I279" t="n">
+        <v>90</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="K279" t="n">
+        <v>3</v>
+      </c>
+      <c r="L279" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29844,19 +30068,19 @@
         <v>256</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.00015</v>
+        <v>0.00018</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.01275</v>
+        <v>0.01336</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -29895,23 +30119,23 @@
         <v>512</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.0032</v>
+        <v>0.00336</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -29946,19 +30170,19 @@
         <v>1024</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.00015</v>
+        <v>0.000167</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.3</v>
+        <v>0.417</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -31430,9 +31654,6 @@
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="n">
-        <v/>
-      </c>
       <c r="J45" t="n">
         <v>5000</v>
       </c>
@@ -31448,6 +31669,109 @@
         <is>
           <t>VERY_LOW</t>
         </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BEMAC Class B — SCL-32 Baseline (5K CW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SCL-32 BLER</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SC BLER</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NN BLER</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>32</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>64</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -31840,7 +32164,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>DONE - 50K CW: NN BLER 0.00018(256), 0.0002(512), 0.00017(1024); SC 50K CW all N</t>
         </is>
       </c>
     </row>
@@ -31951,7 +32275,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>DONE - SCL-32: 0.008(16), 0.0082(32), 0.001(64), 0.0006(128)</t>
         </is>
       </c>
     </row>
@@ -33624,7 +33948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -33919,6 +34243,50 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SCL-32 Baseline</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SCL-32 provides 2-6x improvement over SC for BEMAC Class B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SCL-32 BLER: 0.008(N=16), 0.001(N=64), 0.0006(N=128) vs SC: 0.011, 0.006, 0.002; NN sits between SC and SCL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NN decoder is competitive with SCL at small N but SCL dominates at N&gt;=64</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Extended CW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50K CW confirms NN advantage persists for Class C, with ratio increasing at N=1024</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ratio goes from 0.01 (N=128,256) to 0.06 (N=512) to 0.42 (N=1024); SC BLER=0.0004 at N=1024 now well-measured</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NN decoder still has 2.5x advantage at N=1024 but gap narrows; SC approaches capacity limit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -12311,13 +12311,13 @@
         <v>62</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.0152</v>
+        <v>0.01585</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
@@ -12368,13 +12368,13 @@
         <v>123</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.004567</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -12429,22 +12429,22 @@
         <v>247</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.0012</v>
+        <v>0.00106</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -12490,22 +12490,22 @@
         <v>493</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.0009</v>
+        <v>0.00102</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="M206" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="O206" s="2" t="inlineStr">
@@ -15929,17 +15929,17 @@
         <v>30</v>
       </c>
       <c r="J265" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K265" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L265" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>VERY_LOW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -15990,22 +15990,22 @@
         <v>59</v>
       </c>
       <c r="J266" t="n">
-        <v>0.0008</v>
+        <v>0.002533</v>
       </c>
       <c r="K266" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="L266" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>VERY_LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -16054,14 +16054,14 @@
         <v>0.0002</v>
       </c>
       <c r="K267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L267" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>VERY_LOW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -16112,17 +16112,17 @@
         <v>238</v>
       </c>
       <c r="J268" t="n">
-        <v>0.0008</v>
+        <v>0.000625</v>
       </c>
       <c r="K268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L268" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>VERY_LOW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -31671,7 +31671,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -31868,7 +31867,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>DONE — 20K-50K CW, N&gt;=128 now HIGH confidence</t>
         </is>
       </c>
     </row>
@@ -31979,7 +31978,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>DONE — SC results improved: 8K-20K CW at N&gt;=128, N=256 now HIGH confidence</t>
         </is>
       </c>
     </row>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -9632,25 +9632,29 @@
         <v>71</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0103</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="O156" s="2" t="inlineStr"/>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Extended from 5K to 10K CW</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9689,25 +9693,29 @@
         <v>142</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.0008</v>
+        <v>0.0029</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
-        </is>
-      </c>
-      <c r="O157" s="2" t="inlineStr"/>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Extended from 5K to 10K CW</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9746,22 +9754,22 @@
         <v>284</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.0003333333333333333</v>
+        <v>0.00075</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="M158" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr"/>
@@ -12429,10 +12437,10 @@
         <v>247</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.00106</v>
+        <v>0.0011</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>50000</v>
@@ -12449,7 +12457,7 @@
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>Updated 2026-03-26, was 5000CW</t>
+          <t>Extended to 50K CW</t>
         </is>
       </c>
     </row>
@@ -12490,10 +12498,10 @@
         <v>493</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.00102</v>
+        <v>0.001</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>50000</v>
@@ -12510,7 +12518,7 @@
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>Updated 2026-03-26, was 3000CW</t>
+          <t>Extended to 50K CW</t>
         </is>
       </c>
     </row>
@@ -27980,10 +27988,10 @@
         <v>0.09</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.001</v>
+        <v>0.00106</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>90</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -28157,10 +28165,10 @@
         <v>0.045</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.001</v>
+        <v>0.00106</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -28216,10 +28224,10 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.00102</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>240</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -28629,10 +28637,10 @@
         <v>0.2356666666666667</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.001</v>
+        <v>0.00106</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>235.7</v>
+        <v>222.3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -28688,10 +28696,10 @@
         <v>0.278</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.00102</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>926.7</v>
+        <v>272.5</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -30632,10 +30640,10 @@
         <v>0.037</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.062</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>5000</v>
@@ -30683,10 +30691,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>5000</v>
@@ -30734,10 +30742,10 @@
         <v>0.0444</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.04433333333333334</v>
+        <v>0.0456</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>5000</v>
@@ -30785,10 +30793,10 @@
         <v>0.0324</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.02166666666666667</v>
+        <v>0.0246</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>5000</v>
@@ -30836,16 +30844,16 @@
         <v>0.03266666666666666</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.014</v>
+        <v>0.01585</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
@@ -30854,7 +30862,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -30887,16 +30895,16 @@
         <v>0.0205</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.006</v>
+        <v>0.004567</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3.42</v>
+        <v>4.49</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -30905,7 +30913,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -30938,25 +30946,23 @@
         <v>0.019</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.001</v>
+        <v>0.00106</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19</v>
+        <v>17.92</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
+        <v>50000</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>50000</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -30989,25 +30995,23 @@
         <v>0.014</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.00102</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46.67</v>
+        <v>13.73</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>500</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
+        <v>50000</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>50000</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -31040,10 +31044,10 @@
         <v>0.04</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.046</v>
+        <v>0.0456</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>5000</v>
@@ -31091,10 +31095,10 @@
         <v>0.031</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.025</v>
+        <v>0.0246</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>5000</v>
@@ -31142,16 +31146,16 @@
         <v>0.032</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.015</v>
+        <v>0.01585</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>5000</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
@@ -31193,16 +31197,16 @@
         <v>0.025</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.005</v>
+        <v>0.004567</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>5.47</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>5000</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -31211,7 +31215,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -31244,25 +31248,23 @@
         <v>0.045</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.001</v>
+        <v>0.00106</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45</v>
+        <v>42.45</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
+        <v>50000</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>50000</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -31295,25 +31297,23 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.0003</v>
+        <v>0.00102</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>230</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>500</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
+        <v>50000</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>50000</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -32126,7 +32126,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>PARTIAL — Ru28: N=256 now 10K CW (BLER=0.0103), N=512 10K CW (BLER=0.0029). Ru39: unchanged. N=1024 not finished.</t>
         </is>
       </c>
     </row>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>NCG GMAC 6dB: ratio 0.6 (N=8) -&gt; 46.7 (N=1024)</t>
+          <t>NCG GMAC 6dB: ratio 0.6 (N=8) -&gt; 13.7 (N=1024); MLP ratio 0.87 (N=32) -&gt; 67.7 (N=1024)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BLER Simulations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiments TODO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN vs SC Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +562,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,7 +618,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +674,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -731,7 +730,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -788,7 +786,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -845,7 +842,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -902,7 +898,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -959,7 +954,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1016,7 +1010,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1073,7 +1066,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1130,7 +1122,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1187,7 +1178,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1244,7 +1234,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1301,7 +1290,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1358,7 +1346,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1415,7 +1402,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1472,7 +1458,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1529,7 +1514,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1586,7 +1570,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1643,7 +1626,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1700,7 +1682,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1757,7 +1738,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1814,7 +1794,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1871,7 +1850,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1928,7 +1906,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1985,7 +1962,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2042,7 +2018,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2099,7 +2074,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2156,7 +2130,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2213,7 +2186,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2270,7 +2242,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2327,7 +2298,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2384,7 +2354,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2441,7 +2410,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2498,7 +2466,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2555,7 +2522,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2612,7 +2578,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2669,7 +2634,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2726,7 +2690,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2783,7 +2746,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2840,7 +2802,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2897,7 +2858,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2954,7 +2914,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3011,7 +2970,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3068,7 +3026,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3125,7 +3082,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3182,7 +3138,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3239,7 +3194,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3296,7 +3250,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3353,7 +3306,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3410,7 +3362,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3467,7 +3418,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3524,7 +3474,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3581,7 +3530,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3638,7 +3586,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3695,7 +3642,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3752,7 +3698,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3809,7 +3754,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3866,7 +3810,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3923,7 +3866,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3980,7 +3922,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4037,7 +3978,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4094,7 +4034,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4151,7 +4090,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4208,7 +4146,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4265,7 +4202,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4322,7 +4258,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4379,7 +4314,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4436,7 +4370,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4493,7 +4426,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4550,7 +4482,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4607,7 +4538,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4664,7 +4594,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4721,7 +4650,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4778,7 +4706,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4835,7 +4762,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4892,7 +4818,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4949,7 +4874,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5006,7 +4930,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5063,7 +4986,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8841,7 +8763,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8898,7 +8819,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8955,7 +8875,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9012,7 +8931,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9069,7 +8987,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9126,7 +9043,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9183,7 +9099,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9240,7 +9155,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9297,7 +9211,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9354,7 +9267,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9411,7 +9323,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9468,7 +9379,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9525,7 +9435,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9704,7 +9613,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9761,7 +9669,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9818,7 +9725,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9875,7 +9781,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9932,7 +9837,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10233,7 +10137,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10290,7 +10193,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10347,7 +10249,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10404,7 +10305,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10461,7 +10361,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10518,7 +10417,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10575,7 +10473,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10632,7 +10529,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10689,7 +10585,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10746,7 +10641,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10803,7 +10697,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10860,7 +10753,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10917,7 +10809,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10974,7 +10865,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11031,7 +10921,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11088,7 +10977,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11145,7 +11033,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11202,7 +11089,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11259,7 +11145,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11316,7 +11201,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11373,7 +11257,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11430,7 +11313,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11487,7 +11369,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11544,7 +11425,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11601,7 +11481,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11658,7 +11537,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11715,7 +11593,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11772,7 +11649,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11829,7 +11705,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11886,7 +11761,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11943,7 +11817,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12000,7 +11873,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12057,7 +11929,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12114,7 +11985,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12171,7 +12041,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12228,7 +12097,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12285,7 +12153,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12525,7 +12392,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12582,7 +12448,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12639,7 +12504,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12696,7 +12560,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12753,7 +12616,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12810,7 +12672,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12867,7 +12728,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12924,7 +12784,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12981,7 +12840,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13038,7 +12896,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13095,7 +12952,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13152,7 +13008,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13209,7 +13064,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13266,7 +13120,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13323,7 +13176,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13380,7 +13232,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13437,7 +13288,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13494,7 +13344,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13551,7 +13400,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13608,7 +13456,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13665,7 +13512,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13722,7 +13568,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13779,7 +13624,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13836,7 +13680,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13893,7 +13736,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13950,7 +13792,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14007,7 +13848,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14064,7 +13904,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14121,7 +13960,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14178,7 +14016,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14235,7 +14072,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14292,7 +14128,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14349,7 +14184,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14406,7 +14240,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14463,7 +14296,6 @@
           <t>GOOD</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14520,7 +14352,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14577,7 +14408,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14634,7 +14464,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14691,7 +14520,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14748,7 +14576,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16574,7 +16401,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16631,7 +16457,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="O277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16688,7 +16513,6 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16745,7 +16569,3037 @@
           <t>NEEDS_MORE_CW</t>
         </is>
       </c>
-      <c r="O279" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Est Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P1-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ru48/Rv48 6dB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>More SC CW at N&gt;=256</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Only 1K-3K CW, zero/few errors</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DONE — 20K-50K CW, N&gt;=128 now HIGH confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P1-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ru48/Rv48 6dB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fix NN decoder for GMAC (NCG diverges at large N)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NN/SC ratio grows with N, need new approach</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P1-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ru55/Rv77</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NN decoder for high-rate BEMAC Class B</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No NN results for this rate point</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ru46/Rv23 6dB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SC simulations (only SCL-32 done)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Need SC baseline for comparison</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DONE — SC results improved: 8K-20K CW at N&gt;=128, N=256 now HIGH confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ru33/Rv64 6dB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NN decoder attempts</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>High rate class C, BLER still high at N=1024</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ABNMAC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NN decoder experiments</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No NN results for ABNMAC at all</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ru62/Rv62</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NN decoder</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No NN results for Class A BEMAC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DONE - NN matches SC, ratio 0.47-1.22, generalizes from Class B training</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P3-MEDIUM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ru39/Rv39 3dB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>More CW for SC/SCL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BLER &gt;2% at N=1024, need more data</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P3-MEDIUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ru30/Rv60</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>More NN CW at large N</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Only 20K CW, few errors at N&gt;=512</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DONE - 50K CW: NN BLER 0.00018(256), 0.0002(512), 0.00017(1024); SC 50K CW all N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P3-MEDIUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Frozen set improvements for n&gt;=9</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Many designs have &lt;5K trials at large N</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P4-LOW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3dB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NN decoder for 3dB SNR</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harder channel, may show NN advantage</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P4-LOW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ru50/Rv70</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SCL-32 comparison at all N</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Have NN vs SC but not SCL baseline</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DONE - SCL-32: 0.008(16), 0.0082(32), 0.001(64), 0.0006(128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ru48/Rv48 6dB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Update NN vs SC plots with corrected SC numbers</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SC numbers changed after 50K CW campaign</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DONE - All xlsx/png/pdf updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P3-MEDIUM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ru28/Rv28 3dB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>More SC CW at N=1024</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Only 15 errors/20K CW (MEDIUM)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DONE - 50K CW, 32 errors, HIGH confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P2-HIGH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ru23/Rv46 6dB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>More SC CW at N&gt;=256</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Only 2 errors at N=256, 0 at N&gt;=512</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SNR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ru</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rv</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>NN BLER</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>SC BLER</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN CW</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SC CW</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NN Confidence</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>SC Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>64</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>256</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>512</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03933</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.10967</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00567</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09933</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.296875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="F12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.296875</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6015625</v>
+      </c>
+      <c r="F13" t="n">
+        <v>128</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02455</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.30078125</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6015625</v>
+      </c>
+      <c r="F14" t="n">
+        <v>256</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.30078125</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.599609375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>512</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2998046875</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.599609375</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.000167</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05267</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.15067</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.13133</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.12467</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3515625</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>128</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3515625</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.69921875</v>
+      </c>
+      <c r="F22" t="n">
+        <v>256</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09155000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.349609375</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.69921875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>512</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.349609375</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7001953125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="F27" t="n">
+        <v>32</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.484375</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.484375</v>
+      </c>
+      <c r="F28" t="n">
+        <v>64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.484375</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.484375</v>
+      </c>
+      <c r="F29" t="n">
+        <v>128</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.03267</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.48046875</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.48046875</v>
+      </c>
+      <c r="F30" t="n">
+        <v>256</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.004567</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.482421875</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.482421875</v>
+      </c>
+      <c r="F31" t="n">
+        <v>512</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="I31" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4814453125</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.4814453125</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00102</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="F33" t="n">
+        <v>32</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F34" t="n">
+        <v>64</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F35" t="n">
+        <v>128</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="F36" t="n">
+        <v>256</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.004567</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="F37" t="n">
+        <v>512</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="I37" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B (MLP)</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00102</v>
+      </c>
+      <c r="I38" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F40" t="n">
+        <v>32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F41" t="n">
+        <v>64</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="F42" t="n">
+        <v>128</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="F43" t="n">
+        <v>256</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="F44" t="n">
+        <v>512</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>500</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>VERY_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BEMAC Class B — SCL-32 Baseline (5K CW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SCL-32 BLER</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SC BLER</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NN BLER</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>32</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>64</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -9595,22 +9595,22 @@
         <v>284</v>
       </c>
       <c r="J158" t="n">
-        <v>0.00075</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="K158" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L158" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -13102,22 +13102,22 @@
         <v>117</v>
       </c>
       <c r="J220" t="n">
-        <v>0.001</v>
+        <v>0.00175</v>
       </c>
       <c r="K220" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="L220" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -13158,22 +13158,22 @@
         <v>233</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K221" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L221" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>NEEDS_MORE_CW</t>
         </is>
       </c>
     </row>
@@ -13214,22 +13214,22 @@
         <v>467</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K222" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L222" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>NEEDS_MORE_CW</t>
         </is>
       </c>
     </row>
@@ -14110,22 +14110,22 @@
         <v>654</v>
       </c>
       <c r="J238" t="n">
-        <v>0.027</v>
+        <v>0.0252</v>
       </c>
       <c r="K238" t="n">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="L238" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DONE — SC results improved: 8K-20K CW at N&gt;=128, N=256 now HIGH confidence</t>
+          <t>DONE - N=256: 35/20K HIGH, N=512: 4/20K LOW, N=1024: 4/10K LOW</t>
         </is>
       </c>
     </row>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2 days</t>
+          <t>DONE — SC results improved: 8K-20K CW at N&gt;=128, N=256 now HIGH confidence</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>DONE - Ru28: N=1024 now 50K CW (32 errors, HIGH). Ru39: already HIGH at all N.</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DONE - 50K CW, 32 errors, HIGH confidence</t>
+          <t>DONE - 50K CW, 32 errors, BLER=0.00064, HIGH confidence</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE - N=256: 35/20K HIGH, N=512: 4/20K LOW, N=1024: 4/10K LOW</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -11239,13 +11239,13 @@
         <v>44</v>
       </c>
       <c r="J187" t="n">
-        <v>0.0002</v>
+        <v>0.000385</v>
       </c>
       <c r="K187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L187" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -11351,22 +11351,22 @@
         <v>176</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L189" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -18612,7 +18612,7 @@
         <v>0.0324</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0246</v>
+        <v>0.025</v>
       </c>
       <c r="I28" t="n">
         <v>1.32</v>
@@ -18621,7 +18621,7 @@
         <v>5000</v>
       </c>
       <c r="K28" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>0.0205</v>
       </c>
       <c r="H30" t="n">
-        <v>0.004567</v>
+        <v>0.0046</v>
       </c>
       <c r="I30" t="n">
         <v>4.49</v>
@@ -18723,7 +18723,7 @@
         <v>5000</v>
       </c>
       <c r="K30" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>0.019</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00106</v>
+        <v>0.0011</v>
       </c>
       <c r="I31" t="n">
         <v>17.92</v>
@@ -18816,7 +18816,7 @@
         <v>0.014</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00102</v>
+        <v>0.001</v>
       </c>
       <c r="I32" t="n">
         <v>13.73</v>
@@ -18915,19 +18915,19 @@
         <v>64</v>
       </c>
       <c r="G34" t="n">
-        <v>0.031</v>
+        <v>0.0258</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0246</v>
+        <v>0.025</v>
       </c>
       <c r="I34" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="J34" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="K34" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -18966,16 +18966,16 @@
         <v>128</v>
       </c>
       <c r="G35" t="n">
-        <v>0.032</v>
+        <v>0.0227</v>
       </c>
       <c r="H35" t="n">
         <v>0.01585</v>
       </c>
       <c r="I35" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="J35" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="K35" t="n">
         <v>20000</v>
@@ -19017,19 +19017,19 @@
         <v>256</v>
       </c>
       <c r="G36" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="H36" t="n">
-        <v>0.004567</v>
+        <v>0.0046</v>
       </c>
       <c r="I36" t="n">
-        <v>5.47</v>
+        <v>4.35</v>
       </c>
       <c r="J36" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="K36" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -19071,10 +19071,10 @@
         <v>0.045</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00106</v>
+        <v>0.0011</v>
       </c>
       <c r="I37" t="n">
-        <v>42.45</v>
+        <v>40.91</v>
       </c>
       <c r="J37" t="n">
         <v>5000</v>
@@ -19122,10 +19122,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00102</v>
+        <v>0.001</v>
       </c>
       <c r="I38" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="J38" t="n">
         <v>5000</v>
@@ -19498,6 +19498,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -11407,22 +11407,27 @@
         <v>352</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K190" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L190" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>ZERO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>NEEDS_MORE_CW</t>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Extended from 3K to 10K CW</t>
         </is>
       </c>
     </row>
@@ -12252,10 +12257,10 @@
         <v>247</v>
       </c>
       <c r="J205" t="n">
-        <v>0.0011</v>
+        <v>0.00106</v>
       </c>
       <c r="K205" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L205" t="n">
         <v>50000</v>
@@ -12313,10 +12318,10 @@
         <v>493</v>
       </c>
       <c r="J206" t="n">
-        <v>0.001</v>
+        <v>0.00102</v>
       </c>
       <c r="K206" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L206" t="n">
         <v>50000</v>
@@ -18765,7 +18770,7 @@
         <v>0.019</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0011</v>
+        <v>0.00106</v>
       </c>
       <c r="I31" t="n">
         <v>17.92</v>
@@ -18816,7 +18821,7 @@
         <v>0.014</v>
       </c>
       <c r="H32" t="n">
-        <v>0.001</v>
+        <v>0.00102</v>
       </c>
       <c r="I32" t="n">
         <v>13.73</v>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O279"/>
+  <dimension ref="A1:O284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16572,6 +16572,311 @@
       <c r="N279" t="inlineStr">
         <is>
           <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>SCL-4</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>32</v>
+      </c>
+      <c r="H280" t="n">
+        <v>15</v>
+      </c>
+      <c r="I280" t="n">
+        <v>15</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="K280" t="n">
+        <v>79</v>
+      </c>
+      <c r="L280" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>NEW: fair NN-SCL(L=4) comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>SCL-4</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>64</v>
+      </c>
+      <c r="H281" t="n">
+        <v>31</v>
+      </c>
+      <c r="I281" t="n">
+        <v>31</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="K281" t="n">
+        <v>43</v>
+      </c>
+      <c r="L281" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>NEW: fair NN-SCL(L=4) comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SCL-4</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>128</v>
+      </c>
+      <c r="H282" t="n">
+        <v>62</v>
+      </c>
+      <c r="I282" t="n">
+        <v>62</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K282" t="n">
+        <v>27</v>
+      </c>
+      <c r="L282" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>NEW: fair NN-SCL(L=4) comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>NN-SCL-4</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>256</v>
+      </c>
+      <c r="H283" t="n">
+        <v>123</v>
+      </c>
+      <c r="I283" t="n">
+        <v>123</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="K283" t="n">
+        <v>13</v>
+      </c>
+      <c r="L283" t="n">
+        <v>500</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>NEW: NN-SCL(L=4), 39K param MLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>NN-SCL-4</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>512</v>
+      </c>
+      <c r="H284" t="n">
+        <v>247</v>
+      </c>
+      <c r="I284" t="n">
+        <v>247</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K284" t="n">
+        <v>9</v>
+      </c>
+      <c r="L284" t="n">
+        <v>200</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>NEW: NN-SCL(L=4), 39K param MLP</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17178,6 +17483,43 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>DONE - N=256: 35/20K HIGH, N=512: 4/20K LOW, N=1024: 4/10K LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P1-DONE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ru48/Rv48 6dB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NN-SCL(L=4) at N=256,512 + SCL(L=4) baseline</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Scaling NN-SCL advantage to larger N</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DONE — NN-SCL beats SCL(L=4) at N=32,64 (0.84x,0.89x), loses at N&gt;=128</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19503,7 +19845,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
@@ -19604,6 +19945,233 @@
       </c>
       <c r="E52" t="n">
         <v>5000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="F53" t="n">
+        <v>32</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F54" t="n">
+        <v>64</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="F55" t="n">
+        <v>128</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="F56" t="n">
+        <v>256</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="J56" t="n">
+        <v>500</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6dB</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="F57" t="n">
+        <v>512</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J57" t="n">
+        <v>200</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/RESULTS_AUDIT.xlsx
+++ b/results/RESULTS_AUDIT.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O284"/>
+  <dimension ref="A1:O290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16877,6 +16877,372 @@
       <c r="O284" t="inlineStr">
         <is>
           <t>NEW: NN-SCL(L=4), 39K param MLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>NN-SC</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>32</v>
+      </c>
+      <c r="H285" t="n">
+        <v>16</v>
+      </c>
+      <c r="I285" t="n">
+        <v>22</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="K285" t="n">
+        <v>34</v>
+      </c>
+      <c r="L285" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural, seed=999</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>NN-SCL-4</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>32</v>
+      </c>
+      <c r="H286" t="n">
+        <v>16</v>
+      </c>
+      <c r="I286" t="n">
+        <v>22</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="K286" t="n">
+        <v>22</v>
+      </c>
+      <c r="L286" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural + SCL L=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>NN-SC</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>64</v>
+      </c>
+      <c r="H287" t="n">
+        <v>32</v>
+      </c>
+      <c r="I287" t="n">
+        <v>44</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="K287" t="n">
+        <v>8</v>
+      </c>
+      <c r="L287" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural, seed=999</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>NN-SCL-4</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>64</v>
+      </c>
+      <c r="H288" t="n">
+        <v>32</v>
+      </c>
+      <c r="I288" t="n">
+        <v>44</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="K288" t="n">
+        <v>2</v>
+      </c>
+      <c r="L288" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural + SCL L=4, 8x better than SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>NN-SC</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>128</v>
+      </c>
+      <c r="H289" t="n">
+        <v>64</v>
+      </c>
+      <c r="I289" t="n">
+        <v>89</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural, seed=999</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>NN-SCL-4</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>128</v>
+      </c>
+      <c r="H290" t="n">
+        <v>64</v>
+      </c>
+      <c r="I290" t="n">
+        <v>89</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>NEEDS_MORE_CW</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>ncg_pure_neural + SCL L=4, no gain over NN-SC</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17603,6 +17969,21 @@
           <t>SC Confidence</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NN-SCL4 BLER</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NN-SCL4 vs SC</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>NN-SCL4 CW</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20172,6 +20553,186 @@
         <is>
           <t>LOW</t>
         </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>32</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>64</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BEMAC</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>128</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
